--- a/healthcare_forms/012_health_proxy_authorization_form--healthcare_forms.xlsx
+++ b/healthcare_forms/012_health_proxy_authorization_form--healthcare_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name_1</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,7 +521,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_1</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -544,7 +544,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email_1</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -567,7 +567,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone_1</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>address_1</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -613,7 +613,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zip_1</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>authorized_person_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -659,7 +659,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>relationship_1</t>
+          <t>relationship</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -682,7 +682,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name_3</t>
+          <t>authorized_doctor_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -705,7 +705,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>relationship_2</t>
+          <t>authorized_doctor_relationship</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -728,7 +728,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Your Signature</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name_4</t>
+          <t>authorized_person_signature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -774,7 +774,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>name_5</t>
+          <t>authorized_person_name_print_type</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>relationship_3</t>
+          <t>authorized_person_name_print_type_relationship</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -820,53 +820,53 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>name_6</t>
+          <t>date_of_authorization</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Authorized Person's Name (Print or Type)</t>
+          <t>Date of Authorization</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date_1</t>
+          <t>time_of_authorization</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Time of Authorization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -878,202 +878,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>name_7</t>
+          <t>authorized_person_name_print_type_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Authorized Person's Name (Print or Type)</t>
+          <t>Authorized Person's Name (Print or Type) Time</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>time_1</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>name_8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Authorized Person's Name (Print or Type)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>date_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>name_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Authorized Person's Name (Print or Type)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>name_10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Authorized Person's Name (Print or Type)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>date_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>name_11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Authorized Person's Name (Print or Type)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
